--- a/other/REF_WLC_TX15W_C1-MP A11 15W POWER TRANSMITTER REV04 GERBER/REF_WLC_TX15W_C1-MP A11 15W POWER TRANSMITTER REV05 BOM.xlsx
+++ b/other/REF_WLC_TX15W_C1-MP A11 15W POWER TRANSMITTER REV04 GERBER/REF_WLC_TX15W_C1-MP A11 15W POWER TRANSMITTER REV05 BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20395"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\EPP Transmitter MINI Board\Board Files\REF_WLC_TX15W_C1 Power Transmitter Board\Rev 4\Common mode voltage change\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\neilt\Documents\UNSW\elec3117proj\other\REF_WLC_TX15W_C1-MP A11 15W POWER TRANSMITTER REV04 GERBER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{846E02F4-2F85-4A84-AAB4-44183ED9BC90}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AB4F3BE-EA0C-44B4-9DEE-3C0B78DD119C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="28800" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REF_WLC_TX15W_C1 REV05" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="321">
   <si>
     <t>Item</t>
   </si>
@@ -444,15 +444,6 @@
   </si>
   <si>
     <t>Molex</t>
-  </si>
-  <si>
-    <t>J3</t>
-  </si>
-  <si>
-    <t>MOLEX_2012670005</t>
-  </si>
-  <si>
-    <t>USB-C (USB TYPE-C) USB 3.1 (USB 3.1 Gen 2, Superspeed+) Receptacle Connector 24 Position Surface Mount, Right Angle; Through Hole</t>
   </si>
   <si>
     <t>J4</t>
@@ -1731,7 +1722,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1778,31 +1769,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2221,48 +2191,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:J93"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B2:J92"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="34.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="32.44140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="19.44140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="22.6640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.88671875" style="1"/>
+    <col min="3" max="3" width="8.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="34.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="32.42578125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="19.42578125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="26" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B9" s="26" t="s">
-        <v>303</v>
-      </c>
-      <c r="C9" s="26"/>
-      <c r="D9" s="25" t="s">
-        <v>304</v>
-      </c>
-      <c r="E9" s="25"/>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="26" t="s">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B2" s="19" t="s">
         <v>305</v>
       </c>
-      <c r="C10" s="26"/>
-      <c r="D10" s="35" t="s">
-        <v>313</v>
-      </c>
-      <c r="E10" s="27"/>
-    </row>
-    <row r="12" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="2:10" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="19" t="s">
+        <v>300</v>
+      </c>
+      <c r="C9" s="19"/>
+      <c r="D9" s="18" t="s">
+        <v>301</v>
+      </c>
+      <c r="E9" s="18"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="C10" s="19"/>
+      <c r="D10" s="28" t="s">
+        <v>310</v>
+      </c>
+      <c r="E10" s="20"/>
+    </row>
+    <row r="12" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="2:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B13" s="12" t="s">
         <v>0</v>
       </c>
@@ -2291,7 +2261,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" s="9">
         <v>1</v>
       </c>
@@ -2318,7 +2288,7 @@
       </c>
       <c r="J14" s="10"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="4">
         <v>2</v>
       </c>
@@ -2345,7 +2315,7 @@
       </c>
       <c r="J15" s="3"/>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="4">
         <v>3</v>
       </c>
@@ -2372,7 +2342,7 @@
       </c>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="4">
         <v>4</v>
       </c>
@@ -2399,7 +2369,7 @@
       </c>
       <c r="J17" s="3"/>
     </row>
-    <row r="18" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B18" s="4">
         <v>5</v>
       </c>
@@ -2426,7 +2396,7 @@
       </c>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="4">
         <v>6</v>
       </c>
@@ -2437,23 +2407,23 @@
         <v>65</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="J19" s="3"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="4">
         <v>7</v>
       </c>
@@ -2480,7 +2450,7 @@
       </c>
       <c r="J20" s="3"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="4">
         <v>8</v>
       </c>
@@ -2507,7 +2477,7 @@
       </c>
       <c r="J21" s="3"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="4">
         <v>9</v>
       </c>
@@ -2534,7 +2504,7 @@
       </c>
       <c r="J22" s="3"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="4">
         <v>10</v>
       </c>
@@ -2561,7 +2531,7 @@
       </c>
       <c r="J23" s="3"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="4">
         <v>11</v>
       </c>
@@ -2588,7 +2558,7 @@
       </c>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="4">
         <v>12</v>
       </c>
@@ -2615,7 +2585,7 @@
       </c>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="4">
         <v>13</v>
       </c>
@@ -2642,7 +2612,7 @@
       </c>
       <c r="J26" s="3"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B27" s="4">
         <v>14</v>
       </c>
@@ -2669,7 +2639,7 @@
       </c>
       <c r="J27" s="3"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B28" s="4">
         <v>15</v>
       </c>
@@ -2696,7 +2666,7 @@
       </c>
       <c r="J28" s="3"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B29" s="4">
         <v>16</v>
       </c>
@@ -2723,7 +2693,7 @@
       </c>
       <c r="J29" s="3"/>
     </row>
-    <row r="30" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B30" s="4">
         <v>17</v>
       </c>
@@ -2750,7 +2720,7 @@
       </c>
       <c r="J30" s="3"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="4">
         <v>18</v>
       </c>
@@ -2777,7 +2747,7 @@
       </c>
       <c r="J31" s="3"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="4">
         <v>19</v>
       </c>
@@ -2804,7 +2774,7 @@
       </c>
       <c r="J32" s="3"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="4">
         <v>20</v>
       </c>
@@ -2831,7 +2801,7 @@
       </c>
       <c r="J33" s="3"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="4">
         <v>21</v>
       </c>
@@ -2839,26 +2809,26 @@
         <v>3</v>
       </c>
       <c r="D34" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="E34" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="J34" s="3"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="4">
         <v>22</v>
       </c>
@@ -2866,26 +2836,26 @@
         <v>1</v>
       </c>
       <c r="D35" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I35" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="E35" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>222</v>
-      </c>
       <c r="J35" s="3"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="4">
         <v>23</v>
       </c>
@@ -2893,26 +2863,26 @@
         <v>8</v>
       </c>
       <c r="D36" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="E36" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>226</v>
-      </c>
       <c r="J36" s="3"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="4">
         <v>24</v>
       </c>
@@ -2920,26 +2890,26 @@
         <v>7</v>
       </c>
       <c r="D37" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="E37" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>230</v>
-      </c>
       <c r="J37" s="3"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="4">
         <v>25</v>
       </c>
@@ -2947,26 +2917,26 @@
         <v>1</v>
       </c>
       <c r="D38" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I38" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="E38" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>234</v>
-      </c>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="4">
         <v>26</v>
       </c>
@@ -2974,26 +2944,26 @@
         <v>1</v>
       </c>
       <c r="D39" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I39" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="E39" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>202</v>
-      </c>
       <c r="J39" s="3"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="4">
         <v>27</v>
       </c>
@@ -3001,26 +2971,26 @@
         <v>1</v>
       </c>
       <c r="D40" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I40" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="E40" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>239</v>
-      </c>
       <c r="J40" s="3"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="4">
         <v>28</v>
       </c>
@@ -3028,26 +2998,26 @@
         <v>1</v>
       </c>
       <c r="D41" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I41" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>206</v>
-      </c>
       <c r="J41" s="3"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="4">
         <v>29</v>
       </c>
@@ -3055,26 +3025,26 @@
         <v>1</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="J42" s="3"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="4">
         <v>30</v>
       </c>
@@ -3082,26 +3052,26 @@
         <v>5</v>
       </c>
       <c r="D43" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I43" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>244</v>
-      </c>
       <c r="J43" s="3"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="4">
         <v>31</v>
       </c>
@@ -3109,26 +3079,26 @@
         <v>4</v>
       </c>
       <c r="D44" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>248</v>
-      </c>
       <c r="J44" s="3"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="4">
         <v>32</v>
       </c>
@@ -3136,26 +3106,26 @@
         <v>1</v>
       </c>
       <c r="D45" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I45" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>210</v>
-      </c>
       <c r="J45" s="3"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="4">
         <v>33</v>
       </c>
@@ -3163,26 +3133,26 @@
         <v>1</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E46" s="3">
         <v>0.01</v>
       </c>
       <c r="F46" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="I46" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>254</v>
-      </c>
       <c r="J46" s="3"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="4">
         <v>34</v>
       </c>
@@ -3190,26 +3160,26 @@
         <v>1</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E47" s="3">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="J47" s="3"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="4">
         <v>35</v>
       </c>
@@ -3217,26 +3187,26 @@
         <v>1</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="J48" s="3"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="4">
         <v>36</v>
       </c>
@@ -3244,26 +3214,26 @@
         <v>1</v>
       </c>
       <c r="D49" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I49" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>299</v>
-      </c>
       <c r="J49" s="3"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="4">
         <v>37</v>
       </c>
@@ -3271,26 +3241,26 @@
         <v>1</v>
       </c>
       <c r="D50" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I50" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="E50" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>261</v>
-      </c>
       <c r="J50" s="3"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="4">
         <v>38</v>
       </c>
@@ -3298,26 +3268,26 @@
         <v>4</v>
       </c>
       <c r="D51" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I51" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="E51" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>214</v>
-      </c>
       <c r="J51" s="3"/>
     </row>
-    <row r="52" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B52" s="4">
         <v>39</v>
       </c>
@@ -3344,7 +3314,7 @@
       </c>
       <c r="J52" s="3"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B53" s="4">
         <v>40</v>
       </c>
@@ -3371,7 +3341,7 @@
       </c>
       <c r="J53" s="3"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B54" s="4">
         <v>41</v>
       </c>
@@ -3398,7 +3368,7 @@
       </c>
       <c r="J54" s="3"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="4">
         <v>42</v>
       </c>
@@ -3425,7 +3395,7 @@
       </c>
       <c r="J55" s="3"/>
     </row>
-    <row r="56" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B56" s="4">
         <v>43</v>
       </c>
@@ -3452,7 +3422,7 @@
       </c>
       <c r="J56" s="3"/>
     </row>
-    <row r="57" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B57" s="4">
         <v>44</v>
       </c>
@@ -3479,7 +3449,7 @@
       </c>
       <c r="J57" s="3"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B58" s="4">
         <v>45</v>
       </c>
@@ -3506,171 +3476,171 @@
       </c>
       <c r="J58" s="3"/>
     </row>
-    <row r="59" spans="2:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B59" s="16">
-        <v>46</v>
-      </c>
-      <c r="C59" s="17">
-        <v>1</v>
-      </c>
-      <c r="D59" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="E59" s="17">
-        <v>2012670005</v>
-      </c>
-      <c r="F59" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="G59" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="H59" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="I59" s="17">
-        <v>2012670005</v>
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B59" s="4">
+        <v>47</v>
+      </c>
+      <c r="C59" s="3">
+        <v>1</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>159</v>
       </c>
       <c r="J59" s="3"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B60" s="4">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C60" s="3">
         <v>1</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H60" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="J60" s="3"/>
+    </row>
+    <row r="61" spans="2:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="B61" s="4">
+        <v>49</v>
+      </c>
+      <c r="C61" s="3">
+        <v>1</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="J61" s="3"/>
+    </row>
+    <row r="62" spans="2:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="B62" s="4">
+        <v>50</v>
+      </c>
+      <c r="C62" s="3">
+        <v>1</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="J62" s="3"/>
+    </row>
+    <row r="63" spans="2:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="B63" s="4">
+        <v>51</v>
+      </c>
+      <c r="C63" s="3">
+        <v>6</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="J63" s="3"/>
+    </row>
+    <row r="64" spans="2:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="B64" s="4">
+        <v>52</v>
+      </c>
+      <c r="C64" s="3">
+        <v>1</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="H64" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="J60" s="3"/>
-    </row>
-    <row r="61" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B61" s="4">
-        <v>48</v>
-      </c>
-      <c r="C61" s="3">
-        <v>1</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="J61" s="3"/>
-    </row>
-    <row r="62" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B62" s="4">
-        <v>49</v>
-      </c>
-      <c r="C62" s="3">
-        <v>1</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="J62" s="3"/>
-    </row>
-    <row r="63" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B63" s="4">
-        <v>50</v>
-      </c>
-      <c r="C63" s="3">
-        <v>1</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="J63" s="3"/>
-    </row>
-    <row r="64" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B64" s="4">
-        <v>51</v>
-      </c>
-      <c r="C64" s="3">
-        <v>6</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>117</v>
-      </c>
       <c r="I64" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="J64" s="3"/>
     </row>
-    <row r="65" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B65" s="4">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C65" s="3">
         <v>1</v>
@@ -3679,749 +3649,722 @@
         <v>186</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>48</v>
+        <v>117</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="J65" s="3"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B66" s="4">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C66" s="3">
         <v>1</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>189</v>
+        <v>259</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>190</v>
+        <v>260</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>191</v>
+        <v>261</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>192</v>
+        <v>262</v>
       </c>
       <c r="H66" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="J66" s="3"/>
+    </row>
+    <row r="67" spans="2:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="B67" s="4">
+        <v>55</v>
+      </c>
+      <c r="C67" s="3">
+        <v>1</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="H67" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="J66" s="3"/>
-    </row>
-    <row r="67" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B67" s="4">
-        <v>54</v>
-      </c>
-      <c r="C67" s="3">
-        <v>1</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>266</v>
-      </c>
       <c r="I67" s="3" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="J67" s="3"/>
     </row>
-    <row r="68" spans="2:10" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="B68" s="16">
-        <v>55</v>
-      </c>
-      <c r="C68" s="17">
-        <v>1</v>
-      </c>
-      <c r="D68" s="17" t="s">
+    <row r="68" spans="2:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="B68" s="4">
+        <v>56</v>
+      </c>
+      <c r="C68" s="3">
+        <v>1</v>
+      </c>
+      <c r="D68" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="E68" s="17" t="s">
-        <v>301</v>
-      </c>
-      <c r="F68" s="17" t="s">
+      <c r="E68" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="F68" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="G68" s="17" t="s">
+      <c r="G68" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="H68" s="17" t="s">
+      <c r="H68" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="I68" s="17" t="s">
-        <v>301</v>
+      <c r="I68" s="3" t="s">
+        <v>297</v>
       </c>
       <c r="J68" s="3"/>
     </row>
-    <row r="69" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B69" s="4">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C69" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D69" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I69" s="3">
+        <v>5000</v>
+      </c>
+      <c r="J69" s="3"/>
+    </row>
+    <row r="70" spans="2:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="B70" s="14">
+        <v>58</v>
+      </c>
+      <c r="C70" s="15">
+        <v>3</v>
+      </c>
+      <c r="D70" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="E70" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="F70" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G70" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="H70" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I70" s="15">
+        <v>5001</v>
+      </c>
+      <c r="J70" s="15"/>
+    </row>
+    <row r="71" spans="2:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="11">
+        <v>59</v>
+      </c>
+      <c r="C71" s="6">
+        <v>1</v>
+      </c>
+      <c r="D71" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="E69" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="F69" s="3" t="s">
+      <c r="E71" s="6">
+        <v>831019884</v>
+      </c>
+      <c r="F71" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="I71" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="G69" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="J69" s="3"/>
-    </row>
-    <row r="70" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B70" s="4">
-        <v>57</v>
-      </c>
-      <c r="C70" s="3">
-        <v>3</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I70" s="3">
-        <v>5000</v>
-      </c>
-      <c r="J70" s="3"/>
-    </row>
-    <row r="71" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B71" s="14">
-        <v>58</v>
-      </c>
-      <c r="C71" s="15">
-        <v>3</v>
-      </c>
-      <c r="D71" s="15" t="s">
-        <v>294</v>
-      </c>
-      <c r="E71" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="F71" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G71" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="H71" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I71" s="15">
-        <v>5001</v>
-      </c>
-      <c r="J71" s="15"/>
-    </row>
-    <row r="72" spans="2:10" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="21">
+      <c r="J71" s="6"/>
+    </row>
+    <row r="72" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B72" s="31" t="s">
+        <v>304</v>
+      </c>
+      <c r="C72" s="32"/>
+      <c r="D72" s="32"/>
+      <c r="E72" s="32"/>
+      <c r="F72" s="32"/>
+      <c r="G72" s="32"/>
+      <c r="H72" s="32"/>
+      <c r="I72" s="32"/>
+      <c r="J72" s="33"/>
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B73" s="9">
         <v>59</v>
       </c>
-      <c r="C72" s="19">
-        <v>1</v>
-      </c>
-      <c r="D72" s="19" t="s">
-        <v>273</v>
-      </c>
-      <c r="E72" s="19">
-        <v>831019884</v>
-      </c>
-      <c r="F72" s="19" t="s">
-        <v>275</v>
-      </c>
-      <c r="G72" s="19" t="s">
-        <v>276</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="I72" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="J72" s="6"/>
-    </row>
-    <row r="73" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="38" t="s">
-        <v>307</v>
-      </c>
-      <c r="C73" s="39"/>
-      <c r="D73" s="39"/>
-      <c r="E73" s="39"/>
-      <c r="F73" s="39"/>
-      <c r="G73" s="39"/>
-      <c r="H73" s="39"/>
-      <c r="I73" s="39"/>
-      <c r="J73" s="40"/>
-    </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B74" s="9">
-        <v>59</v>
-      </c>
-      <c r="C74" s="10">
-        <v>1</v>
-      </c>
-      <c r="D74" s="10" t="s">
+      <c r="C73" s="10">
+        <v>1</v>
+      </c>
+      <c r="D73" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="E74" s="10" t="s">
+      <c r="E73" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="F74" s="10" t="s">
+      <c r="F73" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="G74" s="10" t="s">
+      <c r="G73" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="H74" s="10" t="s">
+      <c r="H73" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="I74" s="10" t="s">
+      <c r="I73" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="J74" s="10" t="s">
+      <c r="J73" s="10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B74" s="4">
+        <v>60</v>
+      </c>
+      <c r="C74" s="3">
+        <v>1</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="4">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C75" s="3">
         <v>1</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="J75" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="4">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C76" s="3">
         <v>1</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="4">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C77" s="3">
         <v>1</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>80</v>
+        <v>212</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>81</v>
+        <v>213</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>16</v>
+        <v>180</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>82</v>
+        <v>214</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>18</v>
+        <v>171</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="J77" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="4">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C78" s="3">
         <v>1</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="J78" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="4">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C79" s="3">
         <v>1</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="J79" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B80" s="4">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C80" s="3">
         <v>1</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>249</v>
+        <v>141</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>228</v>
+        <v>142</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>183</v>
+        <v>142</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>229</v>
+        <v>143</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>230</v>
+        <v>142</v>
       </c>
       <c r="J80" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="81" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B81" s="4">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C81" s="3">
         <v>1</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G81" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="I81" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="J81" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="82" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="4">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C82" s="3">
         <v>1</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="J82" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="4">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C83" s="3">
         <v>1</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>156</v>
+        <v>54</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B84" s="4">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C84" s="3">
         <v>1</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="J84" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B85" s="4">
-        <v>71</v>
-      </c>
-      <c r="C85" s="3">
-        <v>1</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="G85" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="H85" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="I85" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="J85" s="3" t="s">
+    <row r="85" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B85" s="11"/>
+      <c r="C85" s="6"/>
+      <c r="D85" s="6"/>
+      <c r="E85" s="6"/>
+      <c r="F85" s="6"/>
+      <c r="G85" s="6"/>
+      <c r="H85" s="6"/>
+      <c r="I85" s="6"/>
+      <c r="J85" s="6"/>
+    </row>
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B86" s="29" t="s">
+        <v>290</v>
+      </c>
+      <c r="C86" s="30"/>
+      <c r="D86" s="30"/>
+      <c r="E86" s="30"/>
+      <c r="F86" s="30"/>
+      <c r="G86" s="30"/>
+      <c r="H86" s="30"/>
+      <c r="I86" s="30"/>
+      <c r="J86" s="8"/>
+    </row>
+    <row r="87" spans="2:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="B87" s="5">
+        <v>1</v>
+      </c>
+      <c r="C87" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row r="86" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B86" s="11"/>
-      <c r="C86" s="6"/>
-      <c r="D86" s="6"/>
-      <c r="E86" s="6"/>
-      <c r="F86" s="6"/>
-      <c r="G86" s="6"/>
-      <c r="H86" s="6"/>
-      <c r="I86" s="6"/>
-      <c r="J86" s="6"/>
-    </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B87" s="36" t="s">
-        <v>293</v>
-      </c>
-      <c r="C87" s="37"/>
-      <c r="D87" s="37"/>
-      <c r="E87" s="37"/>
-      <c r="F87" s="37"/>
-      <c r="G87" s="37"/>
-      <c r="H87" s="37"/>
-      <c r="I87" s="37"/>
-      <c r="J87" s="8"/>
-    </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B88" s="22">
-        <v>1</v>
-      </c>
-      <c r="C88" s="17">
-        <v>8</v>
-      </c>
-      <c r="D88" s="17" t="s">
-        <v>286</v>
-      </c>
-      <c r="E88" s="17" t="s">
-        <v>286</v>
-      </c>
-      <c r="F88" s="23"/>
-      <c r="G88" s="17" t="s">
-        <v>302</v>
-      </c>
-      <c r="H88" s="17" t="s">
-        <v>278</v>
-      </c>
-      <c r="I88" s="24">
+      <c r="D87" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="F87" s="2"/>
+      <c r="G87" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="I87" s="17">
         <v>25512</v>
       </c>
+      <c r="J87" s="2"/>
+    </row>
+    <row r="88" spans="2:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="B88" s="5">
+        <v>2</v>
+      </c>
+      <c r="C88" s="3">
+        <v>4</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="F88" s="2"/>
+      <c r="G88" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="I88" s="3">
+        <v>9530</v>
+      </c>
       <c r="J88" s="2"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:10" ht="30" x14ac:dyDescent="0.25">
       <c r="B89" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C89" s="3">
         <v>4</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F89" s="2"/>
       <c r="G89" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="I89" s="3">
-        <v>9530</v>
+        <v>9330</v>
       </c>
       <c r="J89" s="2"/>
     </row>
-    <row r="90" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C90" s="3">
         <v>4</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F90" s="2"/>
       <c r="G90" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="I90" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="H90" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="I90" s="3">
-        <v>9330</v>
-      </c>
       <c r="J90" s="2"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:10" ht="45" x14ac:dyDescent="0.25">
       <c r="B91" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C91" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F91" s="2"/>
       <c r="G91" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="H91" s="3"/>
+      <c r="I91" s="3"/>
+      <c r="J91" s="2"/>
+    </row>
+    <row r="92" spans="2:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B92" s="16">
+        <v>6</v>
+      </c>
+      <c r="C92" s="6">
+        <v>1</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="F92" s="7"/>
+      <c r="G92" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="H92" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="H91" s="3" t="s">
+      <c r="I92" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="J91" s="2"/>
-    </row>
-    <row r="92" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B92" s="5">
-        <v>5</v>
-      </c>
-      <c r="C92" s="3">
-        <v>1</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="F92" s="2"/>
-      <c r="G92" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="H92" s="3"/>
-      <c r="I92" s="3"/>
-      <c r="J92" s="2"/>
-    </row>
-    <row r="93" spans="2:10" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B93" s="18">
-        <v>6</v>
-      </c>
-      <c r="C93" s="19">
-        <v>1</v>
-      </c>
-      <c r="D93" s="19" t="s">
-        <v>290</v>
-      </c>
-      <c r="E93" s="19" t="s">
-        <v>290</v>
-      </c>
-      <c r="F93" s="20"/>
-      <c r="G93" s="19" t="s">
-        <v>291</v>
-      </c>
-      <c r="H93" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="I93" s="19" t="s">
-        <v>285</v>
-      </c>
-      <c r="J93" s="7"/>
+      <c r="J92" s="7"/>
     </row>
   </sheetData>
-  <sortState ref="C14:J70">
-    <sortCondition ref="D14:D70"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C14:J69">
+    <sortCondition ref="D14:D69"/>
   </sortState>
   <mergeCells count="2">
-    <mergeCell ref="B87:I87"/>
-    <mergeCell ref="B73:J73"/>
+    <mergeCell ref="B86:I86"/>
+    <mergeCell ref="B72:J72"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -4432,50 +4375,50 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:D6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.44140625" customWidth="1"/>
-    <col min="2" max="2" width="12.33203125" customWidth="1"/>
-    <col min="3" max="3" width="17.88671875" customWidth="1"/>
-    <col min="4" max="4" width="67.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" customWidth="1"/>
+    <col min="4" max="4" width="67.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B2" s="28" t="s">
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B2" s="21" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="22" t="s">
+        <v>306</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>307</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B5" s="25">
+        <v>44696</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>303</v>
+      </c>
+      <c r="D5" s="26" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B6" s="25">
+        <v>44984</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="D6" s="26" t="s">
         <v>311</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" s="28" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="29" t="s">
-        <v>309</v>
-      </c>
-      <c r="C4" s="30" t="s">
-        <v>310</v>
-      </c>
-      <c r="D4" s="31" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B5" s="32">
-        <v>44696</v>
-      </c>
-      <c r="C5" s="34" t="s">
-        <v>306</v>
-      </c>
-      <c r="D5" s="33" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B6" s="32">
-        <v>44984</v>
-      </c>
-      <c r="C6" s="34" t="s">
-        <v>313</v>
-      </c>
-      <c r="D6" s="33" t="s">
-        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -4493,12 +4436,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101007578F242160F8849A90FC9149C19D7AF" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="68091ad752778b1b51d8a3aaf82f5f21">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eaef385c-ff42-478c-82bd-5c553085aad6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="771486026ca7a12dfd5047ff83025fdc" ns2:_="">
     <xsd:import namespace="eaef385c-ff42-478c-82bd-5c553085aad6"/>
@@ -4646,6 +4583,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{141FDBF9-3310-4048-8B13-2E6D9EED332F}">
   <ds:schemaRefs>
@@ -4655,22 +4598,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE50C94C-59A6-4B4A-B5A2-F865F2E0FDDB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="eaef385c-ff42-478c-82bd-5c553085aad6"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB7CA430-D971-48A8-AB88-65F50CFBE1FB}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4686,4 +4613,20 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE50C94C-59A6-4B4A-B5A2-F865F2E0FDDB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="eaef385c-ff42-478c-82bd-5c553085aad6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>